--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_unionName.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_unionName.xlsx
@@ -1226,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="12.2857142857143" customWidth="1"/>
@@ -1304,20 +1304,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="3"/>
+    <row r="10" spans="1:2">
+      <c r="B10" s="3"/>
     </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="3"/>
+    <row r="11" spans="1:2">
+      <c r="B11" s="3"/>
     </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="3"/>
+    <row r="12" spans="1:2">
+      <c r="B12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_unionName.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_unionName.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_unionName" sheetId="1" r:id="rId1"/>
@@ -50,19 +50,19 @@
     <t>name</t>
   </si>
   <si>
-    <t>奇迹战魂</t>
+    <t>傲视群雄</t>
   </si>
   <si>
-    <t>大天使之城</t>
+    <t>雷霆问鼎</t>
   </si>
   <si>
-    <t>罗兰大陆</t>
+    <t>焚天逐鹿</t>
   </si>
   <si>
-    <t>血色战神</t>
+    <t>沧澜战歌</t>
   </si>
   <si>
-    <t>欧皇降世</t>
+    <t>逆命征伐</t>
   </si>
 </sst>
 </file>
